--- a/data/sars/pacific/tables/Pacific_2013_Appendix3.xlsx
+++ b/data/sars/pacific/tables/Pacific_2013_Appendix3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/pacific/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E1CB01E-85D3-DF40-9718-B4F504715247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD739526-46A0-D34A-8928-9DB2B3D05A91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1840" yWindow="500" windowWidth="32980" windowHeight="20180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="128">
   <si>
     <t>California sea lion</t>
   </si>
@@ -370,9 +370,6 @@
     <t>survey3</t>
   </si>
   <si>
-    <t>revised</t>
-  </si>
-  <si>
     <t>rf</t>
   </si>
   <si>
@@ -386,6 +383,27 @@
   </si>
   <si>
     <t>≥8.8</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>RF=0.2 in SAR; RF=0.1 was typo in table</t>
+  </si>
+  <si>
+    <t>RF=0.5 in SAR; RF=0.4 was typo in table</t>
+  </si>
+  <si>
+    <t>revision_yr</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>revised this year</t>
+  </si>
+  <si>
+    <t>revised_yn</t>
   </si>
 </sst>
 </file>
@@ -793,7 +811,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P86"/>
+  <dimension ref="A1:R86"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="32.59765625" style="2" bestFit="1" customWidth="1"/>
@@ -808,12 +826,14 @@
     <col min="11" max="11" width="14.19921875" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.3984375" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="15" width="9.3984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="20.796875" style="2" customWidth="1"/>
-    <col min="19" max="16384" width="9" style="2"/>
+    <col min="16" max="16" width="12.796875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="12.59765625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="40.59765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.796875" style="2" customWidth="1"/>
+    <col min="20" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>102</v>
       </c>
@@ -836,7 +856,7 @@
         <v>108</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>109</v>
@@ -860,10 +880,16 @@
         <v>115</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+        <v>124</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -912,8 +938,9 @@
       <c r="P2" s="7">
         <v>2011</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q2" s="7"/>
+    </row>
+    <row r="3" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
@@ -962,8 +989,9 @@
       <c r="P3" s="7">
         <v>2011</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q3" s="7"/>
+    </row>
+    <row r="4" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="8" t="s">
         <v>7</v>
       </c>
@@ -1008,8 +1036,11 @@
       <c r="P4" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q4" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
         <v>7</v>
       </c>
@@ -1054,8 +1085,11 @@
       <c r="P5" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q5" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
         <v>7</v>
       </c>
@@ -1100,8 +1134,11 @@
       <c r="P6" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q6" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
         <v>7</v>
       </c>
@@ -1146,8 +1183,11 @@
       <c r="P7" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q7" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="4" t="s">
         <v>15</v>
       </c>
@@ -1176,10 +1216,10 @@
         <v>4382</v>
       </c>
       <c r="J8" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="K8" s="4" t="s">
         <v>120</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>121</v>
       </c>
       <c r="L8" s="4" t="s">
         <v>6</v>
@@ -1196,8 +1236,9 @@
       <c r="P8" s="7">
         <v>2007</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q8" s="7"/>
+    </row>
+    <row r="9" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="s">
         <v>17</v>
       </c>
@@ -1242,8 +1283,9 @@
       <c r="P9" s="7">
         <v>2000</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q9" s="7"/>
+    </row>
+    <row r="10" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A10" s="8" t="s">
         <v>20</v>
       </c>
@@ -1292,8 +1334,11 @@
       <c r="P10" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q10" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A11" s="8" t="s">
         <v>21</v>
       </c>
@@ -1342,8 +1387,11 @@
       <c r="P11" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q11" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A12" s="8" t="s">
         <v>27</v>
       </c>
@@ -1392,8 +1440,11 @@
       <c r="P12" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q12" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A13" s="8" t="s">
         <v>27</v>
       </c>
@@ -1442,8 +1493,11 @@
       <c r="P13" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q13" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="8" t="s">
         <v>27</v>
       </c>
@@ -1492,8 +1546,11 @@
       <c r="P14" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q14" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="8" t="s">
         <v>27</v>
       </c>
@@ -1542,8 +1599,11 @@
       <c r="P15" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q15" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="8" t="s">
         <v>27</v>
       </c>
@@ -1592,8 +1652,11 @@
       <c r="P16" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q16" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="4" t="s">
         <v>27</v>
       </c>
@@ -1642,8 +1705,9 @@
       <c r="P17" s="7">
         <v>2011</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q17" s="7"/>
+    </row>
+    <row r="18" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="4" t="s">
         <v>37</v>
       </c>
@@ -1692,8 +1756,9 @@
       <c r="P18" s="7">
         <v>2010</v>
       </c>
-    </row>
-    <row r="19" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q18" s="7"/>
+    </row>
+    <row r="19" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="8" t="s">
         <v>40</v>
       </c>
@@ -1742,8 +1807,11 @@
       <c r="P19" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q19" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="4" t="s">
         <v>41</v>
       </c>
@@ -1792,8 +1860,9 @@
       <c r="P20" s="7">
         <v>2010</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q20" s="7"/>
+    </row>
+    <row r="21" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A21" s="4" t="s">
         <v>42</v>
       </c>
@@ -1842,8 +1911,9 @@
       <c r="P21" s="7">
         <v>2008</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q21" s="7"/>
+    </row>
+    <row r="22" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="8" t="s">
         <v>42</v>
       </c>
@@ -1892,8 +1962,11 @@
       <c r="P22" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="23" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q22" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="4" t="s">
         <v>46</v>
       </c>
@@ -1942,8 +2015,9 @@
       <c r="P23" s="7">
         <v>2010</v>
       </c>
-    </row>
-    <row r="24" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q23" s="7"/>
+    </row>
+    <row r="24" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="4" t="s">
         <v>47</v>
       </c>
@@ -1992,8 +2066,9 @@
       <c r="P24" s="7">
         <v>2010</v>
       </c>
-    </row>
-    <row r="25" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q24" s="7"/>
+    </row>
+    <row r="25" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A25" s="4" t="s">
         <v>48</v>
       </c>
@@ -2042,8 +2117,9 @@
       <c r="P25" s="7">
         <v>2012</v>
       </c>
-    </row>
-    <row r="26" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q25" s="7"/>
+    </row>
+    <row r="26" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="4" t="s">
         <v>49</v>
       </c>
@@ -2092,8 +2168,9 @@
       <c r="P26" s="7">
         <v>2010</v>
       </c>
-    </row>
-    <row r="27" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q26" s="7"/>
+    </row>
+    <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="4" t="s">
         <v>50</v>
       </c>
@@ -2142,8 +2219,9 @@
       <c r="P27" s="7">
         <v>2010</v>
       </c>
-    </row>
-    <row r="28" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q27" s="7"/>
+    </row>
+    <row r="28" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="8" t="s">
         <v>50</v>
       </c>
@@ -2192,8 +2270,11 @@
       <c r="P28" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="29" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q28" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="4" t="s">
         <v>54</v>
       </c>
@@ -2216,7 +2297,7 @@
         <v>0.04</v>
       </c>
       <c r="H29" s="13">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="I29" s="13">
         <v>4.5999999999999996</v>
@@ -2242,8 +2323,12 @@
       <c r="P29" s="7">
         <v>2010</v>
       </c>
-    </row>
-    <row r="30" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q29" s="7"/>
+      <c r="R29" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="8" t="s">
         <v>55</v>
       </c>
@@ -2292,8 +2377,11 @@
       <c r="P30" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="31" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q30" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="8" t="s">
         <v>56</v>
       </c>
@@ -2342,8 +2430,11 @@
       <c r="P31" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="32" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q31" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="8" t="s">
         <v>57</v>
       </c>
@@ -2392,8 +2483,11 @@
       <c r="P32" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="33" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q32" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="4" t="s">
         <v>58</v>
       </c>
@@ -2442,8 +2536,9 @@
       <c r="P33" s="7">
         <v>2010</v>
       </c>
-    </row>
-    <row r="34" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q33" s="7"/>
+    </row>
+    <row r="34" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="4" t="s">
         <v>59</v>
       </c>
@@ -2492,8 +2587,9 @@
       <c r="P34" s="7">
         <v>2010</v>
       </c>
-    </row>
-    <row r="35" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q34" s="7"/>
+    </row>
+    <row r="35" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="4" t="s">
         <v>60</v>
       </c>
@@ -2542,8 +2638,9 @@
       <c r="P35" s="7">
         <v>2012</v>
       </c>
-    </row>
-    <row r="36" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q35" s="7"/>
+    </row>
+    <row r="36" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="8" t="s">
         <v>61</v>
       </c>
@@ -2592,8 +2689,11 @@
       <c r="P36" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="37" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q36" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="8" t="s">
         <v>63</v>
       </c>
@@ -2642,8 +2742,11 @@
       <c r="P37" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="38" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q37" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="8" t="s">
         <v>66</v>
       </c>
@@ -2692,8 +2795,11 @@
       <c r="P38" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="39" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q38" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="8" t="s">
         <v>67</v>
       </c>
@@ -2742,8 +2848,11 @@
       <c r="P39" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="40" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q39" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="4" t="s">
         <v>68</v>
       </c>
@@ -2792,8 +2901,9 @@
       <c r="P40" s="7">
         <v>2010</v>
       </c>
-    </row>
-    <row r="41" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q40" s="7"/>
+    </row>
+    <row r="41" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="4" t="s">
         <v>69</v>
       </c>
@@ -2842,8 +2952,9 @@
       <c r="P41" s="7">
         <v>2010</v>
       </c>
-    </row>
-    <row r="42" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q41" s="7"/>
+    </row>
+    <row r="42" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A42" s="8" t="s">
         <v>70</v>
       </c>
@@ -2890,8 +3001,11 @@
       <c r="P42" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="43" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q42" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A43" s="4" t="s">
         <v>70</v>
       </c>
@@ -2940,8 +3054,9 @@
       <c r="P43" s="7">
         <v>2010</v>
       </c>
-    </row>
-    <row r="44" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q43" s="7"/>
+    </row>
+    <row r="44" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A44" s="8" t="s">
         <v>41</v>
       </c>
@@ -2988,8 +3103,11 @@
       <c r="P44" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="45" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q44" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A45" s="8" t="s">
         <v>42</v>
       </c>
@@ -3036,8 +3154,11 @@
       <c r="P45" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="46" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q45" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A46" s="8" t="s">
         <v>42</v>
       </c>
@@ -3086,8 +3207,11 @@
       <c r="P46" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="47" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q46" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A47" s="8" t="s">
         <v>42</v>
       </c>
@@ -3136,8 +3260,11 @@
       <c r="P47" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="48" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q47" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A48" s="8" t="s">
         <v>42</v>
       </c>
@@ -3186,8 +3313,11 @@
       <c r="P48" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="49" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q48" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A49" s="8" t="s">
         <v>42</v>
       </c>
@@ -3236,8 +3366,11 @@
       <c r="P49" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="50" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q49" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A50" s="8" t="s">
         <v>77</v>
       </c>
@@ -3284,8 +3417,11 @@
       <c r="P50" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="51" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q50" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A51" s="8" t="s">
         <v>77</v>
       </c>
@@ -3330,8 +3466,11 @@
       <c r="P51" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="52" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q51" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A52" s="8" t="s">
         <v>77</v>
       </c>
@@ -3376,8 +3515,11 @@
       <c r="P52" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="53" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q52" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A53" s="8" t="s">
         <v>77</v>
       </c>
@@ -3422,8 +3564,11 @@
       <c r="P53" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="54" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q53" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A54" s="8" t="s">
         <v>78</v>
       </c>
@@ -3470,8 +3615,11 @@
       <c r="P54" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="55" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q54" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A55" s="8" t="s">
         <v>78</v>
       </c>
@@ -3520,8 +3668,11 @@
       <c r="P55" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="56" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q55" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A56" s="8" t="s">
         <v>78</v>
       </c>
@@ -3570,8 +3721,11 @@
       <c r="P56" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="57" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q56" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A57" s="8" t="s">
         <v>78</v>
       </c>
@@ -3620,8 +3774,11 @@
       <c r="P57" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="58" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q57" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A58" s="8" t="s">
         <v>78</v>
       </c>
@@ -3668,8 +3825,11 @@
       <c r="P58" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="59" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q58" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A59" s="8" t="s">
         <v>78</v>
       </c>
@@ -3714,8 +3874,11 @@
       <c r="P59" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="60" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q59" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A60" s="4" t="s">
         <v>78</v>
       </c>
@@ -3760,8 +3923,9 @@
       <c r="P60" s="7">
         <v>2010</v>
       </c>
-    </row>
-    <row r="61" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q60" s="7"/>
+    </row>
+    <row r="61" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A61" s="8" t="s">
         <v>46</v>
       </c>
@@ -3808,8 +3972,11 @@
       <c r="P61" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="62" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q61" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A62" s="8" t="s">
         <v>83</v>
       </c>
@@ -3854,10 +4021,16 @@
         <v>2010</v>
       </c>
       <c r="P62" s="10">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+        <v>2013</v>
+      </c>
+      <c r="Q62" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="R62" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A63" s="8" t="s">
         <v>84</v>
       </c>
@@ -3904,8 +4077,11 @@
       <c r="P63" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="64" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q63" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A64" s="8" t="s">
         <v>84</v>
       </c>
@@ -3950,8 +4126,11 @@
       <c r="P64" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="65" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q64" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A65" s="8" t="s">
         <v>87</v>
       </c>
@@ -3998,8 +4177,11 @@
       <c r="P65" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="66" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q65" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A66" s="8" t="s">
         <v>88</v>
       </c>
@@ -4044,8 +4226,11 @@
       <c r="P66" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="67" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q66" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A67" s="8" t="s">
         <v>88</v>
       </c>
@@ -4092,8 +4277,11 @@
       <c r="P67" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="68" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q67" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A68" s="4" t="s">
         <v>88</v>
       </c>
@@ -4138,8 +4326,9 @@
       <c r="P68" s="7">
         <v>2013</v>
       </c>
-    </row>
-    <row r="69" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q68" s="7"/>
+    </row>
+    <row r="69" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A69" s="8" t="s">
         <v>88</v>
       </c>
@@ -4188,8 +4377,11 @@
       <c r="P69" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="70" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q69" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A70" s="4" t="s">
         <v>88</v>
       </c>
@@ -4238,8 +4430,9 @@
       <c r="P70" s="7">
         <v>2010</v>
       </c>
-    </row>
-    <row r="71" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q70" s="7"/>
+    </row>
+    <row r="71" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A71" s="8" t="s">
         <v>50</v>
       </c>
@@ -4286,8 +4479,11 @@
       <c r="P71" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="72" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q71" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A72" s="8" t="s">
         <v>92</v>
       </c>
@@ -4334,8 +4530,11 @@
       <c r="P72" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="73" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q72" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A73" s="8" t="s">
         <v>93</v>
       </c>
@@ -4382,8 +4581,11 @@
       <c r="P73" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="74" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q73" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A74" s="8" t="s">
         <v>94</v>
       </c>
@@ -4430,8 +4632,11 @@
       <c r="P74" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="75" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q74" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A75" s="8" t="s">
         <v>57</v>
       </c>
@@ -4478,8 +4683,11 @@
       <c r="P75" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="76" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q75" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A76" s="8" t="s">
         <v>95</v>
       </c>
@@ -4526,8 +4734,11 @@
       <c r="P76" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="77" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q76" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A77" s="8" t="s">
         <v>59</v>
       </c>
@@ -4574,8 +4785,11 @@
       <c r="P77" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="78" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q77" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A78" s="8" t="s">
         <v>60</v>
       </c>
@@ -4598,7 +4812,7 @@
         <v>0.04</v>
       </c>
       <c r="H78" s="11">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="I78" s="11">
         <v>10.199999999999999</v>
@@ -4622,8 +4836,14 @@
       <c r="P78" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="79" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q78" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="R78" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A79" s="8" t="s">
         <v>66</v>
       </c>
@@ -4670,8 +4890,11 @@
       <c r="P79" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="80" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q79" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A80" s="8" t="s">
         <v>67</v>
       </c>
@@ -4718,8 +4941,11 @@
       <c r="P80" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="81" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q80" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A81" s="8" t="s">
         <v>97</v>
       </c>
@@ -4766,8 +4992,11 @@
       <c r="P81" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="82" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q81" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A82" s="8" t="s">
         <v>68</v>
       </c>
@@ -4814,8 +5043,11 @@
       <c r="P82" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="83" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q82" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A83" s="8" t="s">
         <v>69</v>
       </c>
@@ -4862,8 +5094,11 @@
       <c r="P83" s="10">
         <v>2013</v>
       </c>
-    </row>
-    <row r="84" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q83" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A84" s="4" t="s">
         <v>63</v>
       </c>
@@ -4912,8 +5147,9 @@
       <c r="P84" s="7">
         <v>2009</v>
       </c>
-    </row>
-    <row r="85" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q84" s="7"/>
+    </row>
+    <row r="85" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A85" s="4" t="s">
         <v>98</v>
       </c>
@@ -4942,10 +5178,10 @@
         <v>8</v>
       </c>
       <c r="J85" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K85" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L85" s="4" t="s">
         <v>19</v>
@@ -4962,8 +5198,9 @@
       <c r="P85" s="7">
         <v>2008</v>
       </c>
-    </row>
-    <row r="86" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q85" s="7"/>
+    </row>
+    <row r="86" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A86" s="4" t="s">
         <v>98</v>
       </c>
@@ -4992,10 +5229,10 @@
         <v>11</v>
       </c>
       <c r="J86" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K86" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="L86" s="4" t="s">
         <v>6</v>
@@ -5012,6 +5249,7 @@
       <c r="P86" s="7">
         <v>2008</v>
       </c>
+      <c r="Q86" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
